--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -3469,7 +3469,7 @@
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>5e-07</v>
+        <v>0.1</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -3477,15 +3477,19 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>4e-07</v>
+        <v>0.08</v>
       </c>
       <c r="H67" s="5" t="n">
-        <v>5e-07</v>
+        <v>0.1</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>6e-07</v>
-      </c>
-      <c r="J67" s="3" t="n"/>
+        <v>0.12</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>K_13 = 0.10 g/L: ALS/Pdc pyruvate-affinity ratio (Ilv2/Ilv6 Km 3.9 mM, BRENDA EC 2.2.1.6; Pang &amp; Duggleby 1999 doi:10.1021/bi983013m; Pdc wild-type Km 0.5-1.1 mM, BRENDA EC 4.1.1.1) x r3 half-saturation 0.027 g/L; r13 is Michaelis-Menten since 2026-09-13 (was 5e-7, copied from K_3). +-20% kinetic convention. See docs/reports/r13-rate-law.md</t>
+        </is>
+      </c>
       <c r="K67" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_13 = x</t>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="40.81640625" customWidth="1" min="1" max="1"/>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>0.000264</v>
+        <v>0.017</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -3571,15 +3571,19 @@
         </is>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.0002112</v>
+        <v>0.0136</v>
       </c>
       <c r="H69" s="5" t="n">
-        <v>0.000264</v>
+        <v>0.017</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>0.0003168</v>
-      </c>
-      <c r="J69" s="3" t="n"/>
+        <v>0.0204</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>K_14 = 0.017 g/L: KARI (Ilv5) acetolactate affinity. N. crassa reductoisomerase surrogate Km 0.32 mM (Kiritani et al. 1966 JBC 241:2047; BRENDA EC 1.1.1.86) = 0.042 g/L acetolactate (132.11 g/mol) x in-vivo/in-vitro scale factor S = 0.4 read off Lei's fitted r3/r4/r6 constants (S = 0.27-0.60 / 0.17-0.25 / 0.70). nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.007-0.030 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+        </is>
+      </c>
       <c r="K69" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_14 = x</t>
@@ -3653,7 +3657,7 @@
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0.000264</v>
+        <v>0.08</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -3661,15 +3665,19 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.0002112</v>
+        <v>0.064</v>
       </c>
       <c r="H71" s="5" t="n">
-        <v>0.000264</v>
+        <v>0.08</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>0.0003168</v>
-      </c>
-      <c r="J71" s="3" t="n"/>
+        <v>0.096</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>K_15 = 0.080 g/L: DHAD (Ilv3) DHIV affinity. E. coli IlvD surrogate Km 1.5 mM (Flint et al. 1993 JBC 268:14732; BRENDA EC 4.2.1.9) = 0.201 g/L DHIV (134.13 g/mol) x S = 0.4. nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.034-0.14 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+        </is>
+      </c>
       <c r="K71" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_15 = x</t>
@@ -3743,7 +3751,7 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>0.034</v>
+        <v>0.27</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -3751,15 +3759,19 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.0272</v>
+        <v>0.216</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>0.034</v>
+        <v>0.27</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="J73" s="3" t="n"/>
+        <v>0.324</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>K_16 = 0.27 g/L: Aro10 (the rate-limiting decarboxylase of the lumped KDC + ADH step r16) KIV affinity, Km 8.5 mM (Kneen et al. 2011 FEBS J. 278:1842; BRENDA EC 4.1.1.43), anchored by ratio to r3's Pdc (Km 1.1 mM) exactly as K_13 was, with the molar-mass correction: (8.5/1.1) x 0.302 mM x 116.12 g/mol. r16 is irreversible Michaelis-Menten in KIV since 2026-09-13 (nskinetics b61360e; was 0.034, copied from K_6). +-20% kinetic convention (band 0.27-0.60 for Pdc Km 1.1-0.5 mM is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+        </is>
+      </c>
       <c r="K73" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_16 = x</t>
@@ -3767,54 +3779,53 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>K_16i</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>._k_16ia</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
         <is>
           <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
         </is>
       </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F74" s="3" t="inlineStr">
-        <is>
-          <t>Triangular</t>
-        </is>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>0.0456</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>0.0684</v>
-      </c>
-      <c r="J74" s="3" t="n"/>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_16i = x</t>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>0.02515577165936288</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Triangular</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>0.02012461732749031</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.02515577165936288</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.03018692599123546</v>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_16ia = x</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>._k_16ia</t>
+          <t>._k_16ie</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3833,7 +3844,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.004464538438439914</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3841,59 +3852,15 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.02012461732749031</v>
+        <v>0.003571630750751932</v>
       </c>
       <c r="H75" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.004464538438439914</v>
       </c>
       <c r="I75" t="n">
-        <v>0.03018692599123546</v>
+        <v>0.005357446126127897</v>
       </c>
       <c r="K75" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_16ia = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>._k_16ie</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E76" t="n">
-        <v>0.004464538438439914</v>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>Triangular</t>
-        </is>
-      </c>
-      <c r="G76" t="n">
-        <v>0.003571630750751932</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.004464538438439914</v>
-      </c>
-      <c r="I76" t="n">
-        <v>0.005357446126127897</v>
-      </c>
-      <c r="K76" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_16ie = x</t>
         </is>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="40.81640625" customWidth="1" min="1" max="1"/>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+          <t>Kinetics: Ketoisovalerate-to-Isobutyraldehyde</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+          <t>Kinetics: Ketoisovalerate-to-Isobutyraldehyde</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>K_16 = 0.27 g/L: Aro10 (the rate-limiting decarboxylase of the lumped KDC + ADH step r16) KIV affinity, Km 8.5 mM (Kneen et al. 2011 FEBS J. 278:1842; BRENDA EC 4.1.1.43), anchored by ratio to r3's Pdc (Km 1.1 mM) exactly as K_13 was, with the molar-mass correction: (8.5/1.1) x 0.302 mM x 116.12 g/mol. r16 is irreversible Michaelis-Menten in KIV since 2026-09-13 (nskinetics b61360e; was 0.034, copied from K_6). +-20% kinetic convention (band 0.27-0.60 for Pdc Km 1.1-0.5 mM is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+          <t>K_16 = 0.27 g/L: Aro10 (the rate-limiting decarboxylase of the lumped KDC + ADH step r16) KIV affinity, Km 8.5 mM (Kneen et al. 2011 FEBS J. 278:1842; BRENDA EC 4.1.1.43), anchored by ratio to r3's Pdc (Km 1.1 mM) exactly as K_13 was, with the molar-mass correction: (8.5/1.1) x 0.302 mM x 116.12 g/mol. r16 is irreversible Michaelis-Menten in KIV since 2026-09-13 (nskinetics b61360e; was 0.034, copied from K_6). +-20% kinetic convention (band 0.27-0.60 for Pdc Km 1.1-0.5 mM is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13). Since the 2026-09-15 nskinetics split of the lumped step, r16 is the Aro10 decarboxylation alone (KIV -&gt; isobutyraldehyde + CO2); the Adh6 aldehyde reduction is r17 (k_17, K_17, k_17r, K_17e, k_17ia, k_17ie).</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -3781,12 +3781,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>._k_16ia</t>
+          <t>._k_17ia</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>l_per_g</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3816,21 +3816,26 @@
       <c r="I74" t="n">
         <v>0.03018692599123546</v>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>k_17ia (L/g): acetate cross-product exponential exp(-k_17ia*s_acetate) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ia). The old k_16ia is declared inert (0) in the antimony.</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_16ia = x</t>
+          <t>V406.nsk_kinetic_model._te.k_17ia = x</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>._k_16ie</t>
+          <t>._k_17ie</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3840,7 +3845,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>l_per_g</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3860,9 +3865,210 @@
       <c r="I75" t="n">
         <v>0.005357446126127897</v>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>k_17ie (L/g): ethanol cross-product exponential exp(-k_17ie*s_EtOH) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ie). The old k_16ie is declared inert (0) in the antimony.</t>
+        </is>
+      </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_16ie = x</t>
+          <t>V406.nsk_kinetic_model._te.k_17ie = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>._k_17</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>44</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Triangular</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="H76" t="n">
+        <v>44</v>
+      </c>
+      <c r="I76" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>k_17 = 44 g/L/h: Adh6 (NADPH-dependent aldehyde reductase) capacity for the isobutyraldehyde -&gt; isobutanol step r17 of the 2026-09-15 nskinetics split of the lumped KDC + ADH step. A vmax grounded on the Adh6:Aro10 kcat ratio 296/19 (Adh6 296 s^-1 on 2-methylpropanal + NADPH, Larroy et al. 2002 Biochem. J. 361:163; Aro10 19 s^-1 on KIV, Kneen et al. 2011 FEBS J. 278:1842) x k_16's scenario-B value 2.82 g/L/h. CONSTITUTIVE (not a scenario toggle: the antimony default is 44 in every scenario, incl. A, where it is inert while k_16 = 0), set to keep Adh6 non-limiting at scenario-B flux. +-20 % kinetic convention.</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_17 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>K_17</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>g_per_l</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Triangular</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>0.006880000000000001</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.0086</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.01032</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>K_17 = 0.0086 g/L: Adh6 isobutyraldehyde affinity, K_6 x (0.17/1.1) x (72.11/44.05) -- the Adh6:Adh1 aldehyde-affinity ratio (Adh6 branched-aldehyde Km 0.13-0.21 mM, midpoint 0.17 mM, Larroy et al. 2002 Biochem. J. 361:163; Adh1 acetaldehyde Km 1.1 mM, Ganzhorn et al. 1987 JBC 262:3754) applied to r6's fitted K_6 with the molar-mass correction (isobutyraldehyde 72.11 vs acetaldehyde 44.05 g/mol). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.K_17 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>k_17r</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Triangular</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>0.0002</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00025</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.0003</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>k_17r = 2.5e-4 (dimensionless): the r17 reverse-balance ratio, k_6r/50 -- r6's fitted Adh1 reverse balance scaled by Adh6's ~50-fold aldehyde-over-alcohol preference (Larroy et al. 2002 Biochem. J. 361:163). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_17r = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>K_17e</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Kinetics: Isobutyraldehyde-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>dimensionless</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Triangular</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>K_17e = 0.020 (dimensionless): competitive isobutanol product term of r17, K_17 / Ki_IBO,model with Ki_IBO,model = 0.70 x 50 x 0.17 mM = 0.44 g/L isobutanol (the 0.70 is r6's own in-vitro -&gt; in-vivo transfer factor read off K_6/K_6e; 50 = Adh6's aldehyde-over-alcohol preference, Larroy et al. 2002). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.K_17e = x</t>
         </is>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -1185,19 +1185,21 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>Triangular</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.576</v>
-      </c>
-      <c r="H16" s="3" t="n">
-        <v>0.72</v>
-      </c>
+        <v>0.6840000000000001</v>
+      </c>
+      <c r="H16" s="3" t="n"/>
       <c r="I16" s="3" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="J16" s="3" t="n"/>
+        <v>0.743</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Uniform over the min-max of the 2022-2024 U.S. corn starch content (dry basis) 68.4-74.3 %, U.S. Grains Council, 2024/2025 Corn Harvest Quality Report, https://grains.org/corn_report/corn-harvest-quality-report-2024-2025-2/</t>
+        </is>
+      </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>fixed_F_mass = feedstock.F_mass; feedstock.imass['Starch'] = x * (fixed_F_mass - feedstock.imass['Water']); feedstock.F_mass = fixed_F_mass</t>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>Uniform over the min-max of the 2022-2024 U.S. corn starch content (dry basis) 68.4-74.3 %, U.S. Grains Council, 2024/2025 Corn Harvest Quality Report, https://grains.org/corn_report/corn-harvest-quality-report-2024-2025-2/</t>
+          <t>Uniform over the min-max of the 2022-2024 U.S. corn starch content (dry basis) 68.4-74.3 %, U.S. Grains Council, 2024/2025 Corn Harvest Quality Report, p. 26, https://grains.org/corn_report/corn-harvest-quality-report-2024-2025-2/</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>fixed_F_mass = feedstock.F_mass; feedstock.imass['Starch'] = x * (fixed_F_mass - feedstock.imass['Water']); feedstock.F_mass = fixed_F_mass</t>
+          <t>set_feedstock_starch_content(x)</t>
         </is>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_opt_EtOH_titer.xlsx
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0.04815297959326436</v>
+        <v>2.716581510963849</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -1414,15 +1414,19 @@
         </is>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.03852238367461149</v>
+        <v>2.173265208771079</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.04815297959326436</v>
+        <v>2.716581510963849</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.05778357551191723</v>
-      </c>
-      <c r="J21" s="3" t="n"/>
+        <v>3.259897813156619</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1l = x</t>
@@ -1467,7 +1471,11 @@
       <c r="I22" s="3" t="n">
         <v>1.128</v>
       </c>
-      <c r="J22" s="3" t="n"/>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_1l = x</t>
@@ -1496,7 +1504,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.06932030827859648</v>
+        <v>1.109429092589432</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -1504,15 +1512,19 @@
         </is>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.05545624662287718</v>
+        <v>0.8875432740715455</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.06932030827859648</v>
+        <v>1.109429092589432</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.08318436993431577</v>
-      </c>
-      <c r="J23" s="3" t="n"/>
+        <v>1.331314911107318</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1h = x</t>
@@ -1557,7 +1569,11 @@
       <c r="I24" s="3" t="n">
         <v>0.01392</v>
       </c>
-      <c r="J24" s="3" t="n"/>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_1h = x</t>
@@ -1586,7 +1602,7 @@
         </is>
       </c>
       <c r="E25" s="3" t="n">
-        <v>88.75475886760799</v>
+        <v>89.47621620027783</v>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
@@ -1594,15 +1610,19 @@
         </is>
       </c>
       <c r="G25" s="3" t="n">
-        <v>71.0038070940864</v>
+        <v>71.58097296022227</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>88.75475886760799</v>
+        <v>89.47621620027783</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>106.5057106411296</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
+        <v>107.3714594403334</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1e = x</t>
@@ -1647,7 +1667,11 @@
       <c r="I26" s="3" t="n">
         <v>17.04</v>
       </c>
-      <c r="J26" s="3" t="n"/>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_1i = x</t>
@@ -1692,7 +1716,11 @@
       <c r="I27" s="3" t="n">
         <v>0.144</v>
       </c>
-      <c r="J27" s="3" t="n"/>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_1e = x</t>
@@ -1721,7 +1749,7 @@
         </is>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0.004464538438439914</v>
+        <v>0.015</v>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
@@ -1729,15 +1757,19 @@
         </is>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.003571630750751932</v>
+        <v>0.012</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.004464538438439914</v>
+        <v>0.015</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.005357446126127897</v>
-      </c>
-      <c r="J28" s="3" t="n"/>
+        <v>0.018</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1ie = x</t>
@@ -1766,7 +1798,7 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
@@ -1774,15 +1806,19 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.02012461732749031</v>
+        <v>0.036</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.03018692599123546</v>
-      </c>
-      <c r="J29" s="3" t="n"/>
+        <v>0.054</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1ia = x</t>
@@ -1811,7 +1847,7 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>0.1353664625321014</v>
+        <v>0.09065180915879224</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -1819,15 +1855,19 @@
         </is>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.1082931700256811</v>
+        <v>0.07252144732703379</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.1353664625321014</v>
+        <v>0.09065180915879224</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1624397550385216</v>
-      </c>
-      <c r="J30" s="3" t="n"/>
+        <v>0.1087821709905507</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_1ii = x</t>
@@ -1872,7 +1912,11 @@
       <c r="I31" s="3" t="n">
         <v>0.6012</v>
       </c>
-      <c r="J31" s="3" t="n"/>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_2 = x</t>
@@ -1917,7 +1961,11 @@
       <c r="I32" s="3" t="n">
         <v>0.1212</v>
       </c>
-      <c r="J32" s="3" t="n"/>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_2i = x</t>
@@ -1946,7 +1994,7 @@
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>13.1644632859584</v>
+        <v>3.58469294989378</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -1954,15 +2002,19 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>10.53157062876672</v>
+        <v>2.867754359915024</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>13.1644632859584</v>
+        <v>3.58469294989378</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>15.79735594315008</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
+        <v>4.301631539872536</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_3 = x</t>
@@ -2007,7 +2059,11 @@
       <c r="I34" s="5" t="n">
         <v>6e-07</v>
       </c>
-      <c r="J34" s="3" t="n"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_3 = x</t>
@@ -2052,7 +2108,11 @@
       <c r="I35" s="3" t="n">
         <v>5.76</v>
       </c>
-      <c r="J35" s="3" t="n"/>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_4 = x</t>
@@ -2081,7 +2141,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2089,15 +2149,19 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.007143261501503863</v>
+        <v>0.024</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.01071489225225579</v>
-      </c>
-      <c r="J36" s="3" t="n"/>
+        <v>0.036</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_4ie = x</t>
@@ -2126,7 +2190,7 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2134,15 +2198,19 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.04024923465498062</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.06037385198247092</v>
-      </c>
-      <c r="J37" s="3" t="n"/>
+        <v>0.108</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_4ia = x</t>
@@ -2171,7 +2239,7 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2179,15 +2247,19 @@
         </is>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2165863400513622</v>
+        <v>0.1450428946540676</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.3248795100770432</v>
-      </c>
-      <c r="J38" s="3" t="n"/>
+        <v>0.2175643419811014</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_4ii = x</t>
@@ -2232,7 +2304,11 @@
       <c r="I39" s="3" t="n">
         <v>0.0003168</v>
       </c>
-      <c r="J39" s="3" t="n"/>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_4 = x</t>
@@ -2277,7 +2353,11 @@
       <c r="I40" s="3" t="n">
         <v>0.01248</v>
       </c>
-      <c r="J40" s="3" t="n"/>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_5 = x</t>
@@ -2322,7 +2402,11 @@
       <c r="I41" s="3" t="n">
         <v>0.01224</v>
       </c>
-      <c r="J41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_5 = x</t>
@@ -2367,7 +2451,11 @@
       <c r="I42" s="3" t="n">
         <v>0.9299999999999999</v>
       </c>
-      <c r="J42" s="3" t="n"/>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_5e = x</t>
@@ -2412,7 +2500,11 @@
       <c r="I43" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="J43" s="3" t="n"/>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_5e = x</t>
@@ -2457,7 +2549,11 @@
       <c r="I44" s="3" t="n">
         <v>528</v>
       </c>
-      <c r="J44" s="3" t="n"/>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_5i = x</t>
@@ -2486,7 +2582,7 @@
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>23.93360676928758</v>
+        <v>3.486966718157523</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2494,15 +2590,19 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>19.14688541543007</v>
+        <v>2.789573374526019</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>23.93360676928758</v>
+        <v>3.486966718157523</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>28.7203281231451</v>
-      </c>
-      <c r="J45" s="3" t="n"/>
+        <v>4.184360061789027</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_6 = x</t>
@@ -2547,7 +2647,11 @@
       <c r="I46" s="3" t="n">
         <v>0.0408</v>
       </c>
-      <c r="J46" s="3" t="n"/>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_6 = x</t>
@@ -2592,7 +2696,11 @@
       <c r="I47" s="3" t="n">
         <v>0.0684</v>
       </c>
-      <c r="J47" s="3" t="n"/>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K47" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_6e = x</t>
@@ -2621,7 +2729,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2629,13 +2737,18 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0.02012461732749031</v>
+        <v>0.036</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="I48" t="n">
-        <v>0.03018692599123546</v>
+        <v>0.054</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -2665,7 +2778,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.1353664625321014</v>
+        <v>0.09065180915879224</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2673,13 +2786,18 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>0.1082931700256811</v>
+        <v>0.07252144732703379</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1353664625321014</v>
+        <v>0.09065180915879224</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1624397550385216</v>
+        <v>0.1087821709905507</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -2725,7 +2843,11 @@
       <c r="I50" s="3" t="n">
         <v>1.4436</v>
       </c>
-      <c r="J50" s="3" t="n"/>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_7 = x</t>
@@ -2754,7 +2876,7 @@
         </is>
       </c>
       <c r="E51" s="3" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -2762,15 +2884,19 @@
         </is>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.007143261501503863</v>
+        <v>0.024</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.01071489225225579</v>
-      </c>
-      <c r="J51" s="3" t="n"/>
+        <v>0.036</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K51" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_7ie = x</t>
@@ -2799,7 +2925,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -2807,15 +2933,19 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.04024923465498062</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.06037385198247092</v>
-      </c>
-      <c r="J52" s="3" t="n"/>
+        <v>0.108</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_7ia = x</t>
@@ -2844,7 +2974,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -2852,15 +2982,19 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2165863400513622</v>
+        <v>0.1450428946540676</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.3248795100770432</v>
-      </c>
-      <c r="J53" s="3" t="n"/>
+        <v>0.2175643419811014</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K53" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_7ii = x</t>
@@ -2905,7 +3039,11 @@
       <c r="I54" s="3" t="n">
         <v>0.01212</v>
       </c>
-      <c r="J54" s="3" t="n"/>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_7 = x</t>
@@ -2950,7 +3088,11 @@
       <c r="I55" s="3" t="n">
         <v>0.7068</v>
       </c>
-      <c r="J55" s="3" t="n"/>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K55" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_8 = x</t>
@@ -2995,7 +3137,11 @@
       <c r="I56" s="3" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="J56" s="3" t="n"/>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_9 = x</t>
@@ -3040,7 +3186,11 @@
       <c r="I57" s="3" t="n">
         <v>0.09011999999999999</v>
       </c>
-      <c r="J57" s="3" t="n"/>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K57" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_9e = x</t>
@@ -3085,7 +3235,11 @@
       <c r="I58" s="3" t="n">
         <v>15.6</v>
       </c>
-      <c r="J58" s="3" t="n"/>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_9e = x</t>
@@ -3130,7 +3284,11 @@
       <c r="I59" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="J59" s="3" t="n"/>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K59" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.K_9i = x</t>
@@ -3175,7 +3333,11 @@
       <c r="I60" s="3" t="n">
         <v>0.004788</v>
       </c>
-      <c r="J60" s="3" t="n"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_9c = x</t>
@@ -3220,7 +3382,11 @@
       <c r="I61" s="3" t="n">
         <v>0.07199999999999999</v>
       </c>
-      <c r="J61" s="3" t="n"/>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K61" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_10 = x</t>
@@ -3249,7 +3415,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3257,13 +3423,18 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>0.007143261501503863</v>
+        <v>0.024</v>
       </c>
       <c r="H62" t="n">
-        <v>0.008929076876879828</v>
+        <v>0.03</v>
       </c>
       <c r="I62" t="n">
-        <v>0.01071489225225579</v>
+        <v>0.036</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -3293,7 +3464,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -3301,13 +3472,18 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>0.04024923465498062</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0.05031154331872577</v>
+        <v>0.09</v>
       </c>
       <c r="I63" t="n">
-        <v>0.06037385198247092</v>
+        <v>0.108</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -3337,7 +3513,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -3345,13 +3521,18 @@
         </is>
       </c>
       <c r="G64" t="n">
-        <v>0.2165863400513622</v>
+        <v>0.1450428946540676</v>
       </c>
       <c r="H64" t="n">
-        <v>0.2707329250642027</v>
+        <v>0.1813036183175845</v>
       </c>
       <c r="I64" t="n">
-        <v>0.3248795100770432</v>
+        <v>0.2175643419811014</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -3397,7 +3578,11 @@
       <c r="I65" s="3" t="n">
         <v>0.024</v>
       </c>
-      <c r="J65" s="3" t="n"/>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K65" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_11 = x</t>
@@ -3426,7 +3611,7 @@
         </is>
       </c>
       <c r="E66" s="3" t="n">
-        <v>0.02446841383095393</v>
+        <v>0.001</v>
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
@@ -3434,15 +3619,19 @@
         </is>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.01957473106476314</v>
+        <v>0.0008000000000000003</v>
       </c>
       <c r="H66" s="5" t="n">
-        <v>0.02446841383095393</v>
+        <v>0.001</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>0.02936209659714471</v>
-      </c>
-      <c r="J66" s="3" t="n"/>
+        <v>0.0012</v>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_13 = x</t>
@@ -3479,7 +3668,7 @@
         </is>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.08</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="H67" s="5" t="n">
         <v>0.1</v>
@@ -3489,7 +3678,7 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
-          <t>K_13 = 0.10 g/L: ALS/Pdc pyruvate-affinity ratio (Ilv2/Ilv6 Km 3.9 mM, BRENDA EC 2.2.1.6; Pang &amp; Duggleby 1999 doi:10.1021/bi983013m; Pdc wild-type Km 0.5-1.1 mM, BRENDA EC 4.1.1.1) x r3 half-saturation 0.027 g/L; r13 is Michaelis-Menten since 2026-09-13 (was 5e-7, copied from K_3). +-20% kinetic convention. See docs/reports/r13-rate-law.md</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_13 = 0.10 g/L: ALS/Pdc pyruvate-affinity ratio (Ilv2/Ilv6 Km 3.9 mM, BRENDA EC 2.2.1.6; Pang &amp; Duggleby 1999 doi:10.1021/bi983013m; Pdc wild-type Km 0.5-1.1 mM, BRENDA EC 4.1.1.1) x r3 half-saturation 0.027 g/L; r13 is Michaelis-Menten since 2026-09-13 (was 5e-7, copied from K_3). +-20% kinetic convention. See docs/reports/r13-rate-law.md</t>
         </is>
       </c>
       <c r="K67" s="3" t="inlineStr">
@@ -3520,7 +3709,7 @@
         </is>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0.01178036029472138</v>
+        <v>0.001</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -3528,15 +3717,19 @@
         </is>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.009424288235777107</v>
+        <v>0.0008000000000000003</v>
       </c>
       <c r="H68" s="5" t="n">
-        <v>0.01178036029472138</v>
+        <v>0.001</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>0.01413643235366566</v>
-      </c>
-      <c r="J68" s="3" t="n"/>
+        <v>0.0012</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_14 = x</t>
@@ -3583,7 +3776,7 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>K_14 = 0.017 g/L: KARI (Ilv5) acetolactate affinity. N. crassa reductoisomerase surrogate Km 0.32 mM (Kiritani et al. 1966 JBC 241:2047; BRENDA EC 1.1.1.86) = 0.042 g/L acetolactate (132.11 g/mol) x in-vivo/in-vitro scale factor S = 0.4 read off Lei's fitted r3/r4/r6 constants (S = 0.27-0.60 / 0.17-0.25 / 0.70). nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.007-0.030 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_14 = 0.017 g/L: KARI (Ilv5) acetolactate affinity. N. crassa reductoisomerase surrogate Km 0.32 mM (Kiritani et al. 1966 JBC 241:2047; BRENDA EC 1.1.1.86) = 0.042 g/L acetolactate (132.11 g/mol) x in-vivo/in-vitro scale factor S = 0.4 read off Lei's fitted r3/r4/r6 constants (S = 0.27-0.60 / 0.17-0.25 / 0.70). nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.007-0.030 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
         </is>
       </c>
       <c r="K69" s="3" t="inlineStr">
@@ -3614,7 +3807,7 @@
         </is>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0.006854380625979275</v>
+        <v>0.001015</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -3622,15 +3815,19 @@
         </is>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.00548350450078342</v>
+        <v>0.0008120000000000001</v>
       </c>
       <c r="H70" s="5" t="n">
-        <v>0.006854380625979275</v>
+        <v>0.001015</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>0.008225256751175129</v>
-      </c>
-      <c r="J70" s="3" t="n"/>
+        <v>0.001218</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_15 = x</t>
@@ -3677,7 +3874,7 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
-          <t>K_15 = 0.080 g/L: DHAD (Ilv3) DHIV affinity. E. coli IlvD surrogate Km 1.5 mM (Flint et al. 1993 JBC 268:14732; BRENDA EC 4.2.1.9) = 0.201 g/L DHIV (134.13 g/mol) x S = 0.4. nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.034-0.14 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_15 = 0.080 g/L: DHAD (Ilv3) DHIV affinity. E. coli IlvD surrogate Km 1.5 mM (Flint et al. 1993 JBC 268:14732; BRENDA EC 4.2.1.9) = 0.201 g/L DHIV (134.13 g/mol) x S = 0.4. nskinetics b61360e, 2026-09-13 (was 2.64e-4, copied from K_4). +-20% kinetic convention (band over the S range 0.034-0.14 is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13).</t>
         </is>
       </c>
       <c r="K71" s="3" t="inlineStr">
@@ -3708,7 +3905,7 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>0.05443358495990275</v>
+        <v>0.0008789900000000002</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -3716,15 +3913,19 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.0435468679679222</v>
+        <v>0.0007031920000000002</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>0.05443358495990275</v>
+        <v>0.0008789900000000002</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>0.06532030195188331</v>
-      </c>
-      <c r="J72" s="3" t="n"/>
+        <v>0.001054788</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py)</t>
+        </is>
+      </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_16 = x</t>
@@ -3771,7 +3972,7 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
-          <t>K_16 = 0.27 g/L: Aro10 (the rate-limiting decarboxylase of the lumped KDC + ADH step r16) KIV affinity, Km 8.5 mM (Kneen et al. 2011 FEBS J. 278:1842; BRENDA EC 4.1.1.43), anchored by ratio to r3's Pdc (Km 1.1 mM) exactly as K_13 was, with the molar-mass correction: (8.5/1.1) x 0.302 mM x 116.12 g/mol. r16 is irreversible Michaelis-Menten in KIV since 2026-09-13 (nskinetics b61360e; was 0.034, copied from K_6). +-20% kinetic convention (band 0.27-0.60 for Pdc Km 1.1-0.5 mM is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13). Since the 2026-09-15 nskinetics split of the lumped step, r16 is the Aro10 decarboxylation alone (KIV -&gt; isobutyraldehyde + CO2); the Adh6 aldehyde reduction is r17 (k_17, K_17, k_17r, K_17e, k_17ia, k_17ie).</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_16 = 0.27 g/L: Aro10 (the rate-limiting decarboxylase of the lumped KDC + ADH step r16) KIV affinity, Km 8.5 mM (Kneen et al. 2011 FEBS J. 278:1842; BRENDA EC 4.1.1.43), anchored by ratio to r3's Pdc (Km 1.1 mM) exactly as K_13 was, with the molar-mass correction: (8.5/1.1) x 0.302 mM x 116.12 g/mol. r16 is irreversible Michaelis-Menten in KIV since 2026-09-13 (nskinetics b61360e; was 0.034, copied from K_6). +-20% kinetic convention (band 0.27-0.60 for Pdc Km 1.1-0.5 mM is for a dedicated sweep only). See nskinetics docs/reports/r14-r16-rate-laws-and-affinity-anchoring.md (2026-09-13). Since the 2026-09-15 nskinetics split of the lumped step, r16 is the Aro10 decarboxylation alone (KIV -&gt; isobutyraldehyde + CO2); the Adh6 aldehyde reduction is r17 (k_17, K_17, k_17r, K_17e, k_17ia, k_17ie).</t>
         </is>
       </c>
       <c r="K73" s="3" t="inlineStr">
@@ -3802,7 +4003,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -3810,17 +4011,17 @@
         </is>
       </c>
       <c r="G74" t="n">
-        <v>0.02012461732749031</v>
+        <v>0.036</v>
       </c>
       <c r="H74" t="n">
-        <v>0.02515577165936288</v>
+        <v>0.045</v>
       </c>
       <c r="I74" t="n">
-        <v>0.03018692599123546</v>
+        <v>0.054</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>k_17ia (L/g): acetate cross-product exponential exp(-k_17ia*s_acetate) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ia). The old k_16ia is declared inert (0) in the antimony.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: k_17ia (L/g): acetate cross-product exponential exp(-k_17ia*s_acetate) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ia). The old k_16ia is declared inert (0) in the antimony.</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -3851,7 +4052,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.004464538438439914</v>
+        <v>0.015</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -3859,17 +4060,17 @@
         </is>
       </c>
       <c r="G75" t="n">
-        <v>0.003571630750751932</v>
+        <v>0.012</v>
       </c>
       <c r="H75" t="n">
-        <v>0.004464538438439914</v>
+        <v>0.015</v>
       </c>
       <c r="I75" t="n">
-        <v>0.005357446126127897</v>
+        <v>0.018</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>k_17ie (L/g): ethanol cross-product exponential exp(-k_17ie*s_EtOH) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ie). The old k_16ie is declared inert (0) in the antimony.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: k_17ie (L/g): ethanol cross-product exponential exp(-k_17ie*s_EtOH) on the alcohol-forming step r17 -- the lumped r16's coefficient re-homed by the 2026-09-15 nskinetics split (value unchanged; symmetric with r6's k_6ie). The old k_16ie is declared inert (0) in the antimony.</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -3900,7 +4101,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>44</v>
+        <v>2.154</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -3908,17 +4109,17 @@
         </is>
       </c>
       <c r="G76" t="n">
-        <v>35.2</v>
+        <v>1.7232</v>
       </c>
       <c r="H76" t="n">
-        <v>44</v>
+        <v>2.154</v>
       </c>
       <c r="I76" t="n">
-        <v>52.8</v>
+        <v>2.5848</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>k_17 = 44 g/L/h: Adh6 (NADPH-dependent aldehyde reductase) capacity for the isobutyraldehyde -&gt; isobutanol step r17 of the 2026-09-15 nskinetics split of the lumped KDC + ADH step. A vmax grounded on the Adh6:Aro10 kcat ratio 296/19 (Adh6 296 s^-1 on 2-methylpropanal + NADPH, Larroy et al. 2002 Biochem. J. 361:163; Aro10 19 s^-1 on KIV, Kneen et al. 2011 FEBS J. 278:1842) x k_16's scenario-B value 2.82 g/L/h. CONSTITUTIVE (not a scenario toggle: the antimony default is 44 in every scenario, incl. A, where it is inert while k_16 = 0), set to keep Adh6 non-limiting at scenario-B flux. +-20 % kinetic convention.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: k_17 = 44 g/L/h: Adh6 (NADPH-dependent aldehyde reductase) capacity for the isobutyraldehyde -&gt; isobutanol step r17 of the 2026-09-15 nskinetics split of the lumped KDC + ADH step. A vmax grounded on the Adh6:Aro10 kcat ratio 296/19 (Adh6 296 s^-1 on 2-methylpropanal + NADPH, Larroy et al. 2002 Biochem. J. 361:163; Aro10 19 s^-1 on KIV, Kneen et al. 2011 FEBS J. 278:1842) x k_16's scenario-B value 2.82 g/L/h. CONSTITUTIVE (not a scenario toggle: the antimony default is 44 in every scenario, incl. A, where it is inert while k_16 = 0), set to keep Adh6 non-limiting at scenario-B flux. +-20 % kinetic convention.</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -3967,7 +4168,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>K_17 = 0.0086 g/L: Adh6 isobutyraldehyde affinity, K_6 x (0.17/1.1) x (72.11/44.05) -- the Adh6:Adh1 aldehyde-affinity ratio (Adh6 branched-aldehyde Km 0.13-0.21 mM, midpoint 0.17 mM, Larroy et al. 2002 Biochem. J. 361:163; Adh1 acetaldehyde Km 1.1 mM, Ganzhorn et al. 1987 JBC 262:3754) applied to r6's fitted K_6 with the molar-mass correction (isobutyraldehyde 72.11 vs acetaldehyde 44.05 g/mol). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_17 = 0.0086 g/L: Adh6 isobutyraldehyde affinity, K_6 x (0.17/1.1) x (72.11/44.05) -- the Adh6:Adh1 aldehyde-affinity ratio (Adh6 branched-aldehyde Km 0.13-0.21 mM, midpoint 0.17 mM, Larroy et al. 2002 Biochem. J. 361:163; Adh1 acetaldehyde Km 1.1 mM, Ganzhorn et al. 1987 JBC 262:3754) applied to r6's fitted K_6 with the molar-mass correction (isobutyraldehyde 72.11 vs acetaldehyde 44.05 g/mol). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -4016,7 +4217,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>k_17r = 2.5e-4 (dimensionless): the r17 reverse-balance ratio, k_6r/50 -- r6's fitted Adh1 reverse balance scaled by Adh6's ~50-fold aldehyde-over-alcohol preference (Larroy et al. 2002 Biochem. J. 361:163). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: k_17r = 2.5e-4 (dimensionless): the r17 reverse-balance ratio, k_6r/50 -- r6's fitted Adh1 reverse balance scaled by Adh6's ~50-fold aldehyde-over-alcohol preference (Larroy et al. 2002 Biochem. J. 361:163). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -4065,7 +4266,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>K_17e = 0.020 (dimensionless): competitive isobutanol product term of r17, K_17 / Ki_IBO,model with Ki_IBO,model = 0.70 x 50 x 0.17 mM = 0.44 g/L isobutanol (the 0.70 is r6's own in-vitro -&gt; in-vivo transfer factor read off K_6/K_6e; 50 = Adh6's aldehyde-over-alcohol preference, Larroy et al. 2002). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
+          <t>opt_EtOH_titer: trial 1820 of kin_opt_ethanol_isobutanol_metabolic_split_12d_etoh_titer_gp_rb0.001-4_ib0.75-1.5_aA_rs350_burden (anchor scenario A; build_opt_split12d_workbooks.py) | template note: K_17e = 0.020 (dimensionless): competitive isobutanol product term of r17, K_17 / Ki_IBO,model with Ki_IBO,model = 0.70 x 50 x 0.17 mM = 0.44 g/L isobutanol (the 0.70 is r6's own in-vitro -&gt; in-vivo transfer factor read off K_6/K_6e; 50 = Adh6's aldehyde-over-alcohol preference, Larroy et al. 2002). nskinetics 2026-09-15 split. +-20 % kinetic convention.</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
